--- a/KaizhongRPA/bin/Debug/config/RpaGroup/工艺路线导入.xlsx
+++ b/KaizhongRPA/bin/Debug/config/RpaGroup/工艺路线导入.xlsx
@@ -187,10 +187,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SJXZ.2024</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>xujunren@kaizhong.com;tanxianzhong@kaizhong.com</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -256,6 +252,10 @@
   </si>
   <si>
     <t>07d38e8f-a858-4283-9827-0039032c9f95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SJZ2026</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +724,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
@@ -823,7 +823,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>26</v>
@@ -845,7 +845,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>35</v>
@@ -875,24 +875,24 @@
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -900,7 +900,7 @@
         <v>30</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>31</v>
@@ -911,10 +911,10 @@
         <v>32</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -922,21 +922,21 @@
         <v>33</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
